--- a/output/ARKK/00_Starter_Residual_2.5_to_5pct/ARKK_starter_residual_analysis.xlsx
+++ b/output/ARKK/00_Starter_Residual_2.5_to_5pct/ARKK_starter_residual_analysis.xlsx
@@ -534,31 +534,31 @@
         <v>55.55555555555556</v>
       </c>
       <c r="G2" t="n">
-        <v>1064.944444444444</v>
+        <v>1067.388888888889</v>
       </c>
       <c r="H2" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I2" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>89.65517241379311</v>
+        <v>89.84962406015038</v>
       </c>
       <c r="M2" t="n">
-        <v>115.4789272030651</v>
+        <v>121.0488721804511</v>
       </c>
       <c r="N2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2" t="n">
-        <v>510.2027027027027</v>
+        <v>558.28</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +723,7 @@
         <v>7.843251035834591</v>
       </c>
       <c r="E5" t="n">
-        <v>3.011860975600977</v>
+        <v>2.943761256716523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="E8" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>3.714629452316109</v>
       </c>
       <c r="E9" t="n">
-        <v>1.370114791547245</v>
+        <v>1.117131813989466</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3954</v>
+        <v>3998</v>
       </c>
       <c r="H9" t="n">
-        <v>3954</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="10">
@@ -933,7 +933,7 @@
         <v>6.728028039408759</v>
       </c>
       <c r="E12" t="n">
-        <v>1.282884978605355</v>
+        <v>1.139081242331629</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="E18" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I262"/>
+  <dimension ref="A1:I267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,7 +1471,7 @@
         <v>6.321154281486645</v>
       </c>
       <c r="G9" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>6.016132899190522</v>
       </c>
       <c r="G10" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>6.016132899190522</v>
       </c>
       <c r="G11" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>5.11774291919013</v>
       </c>
       <c r="G12" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>5.11774291919013</v>
       </c>
       <c r="G13" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>5.11774291919013</v>
       </c>
       <c r="G14" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>5.11774291919013</v>
       </c>
       <c r="G15" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>4.823016586376455</v>
       </c>
       <c r="G16" t="n">
-        <v>1.748509665332456</v>
+        <v>1.459313160654627</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2969</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="17">
@@ -1735,7 +1735,7 @@
         <v>5.040960864493372</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.3240085555167544</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1768,15 +1768,15 @@
         <v>4.988446123760042</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.3240085555167544</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>769</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="19">
@@ -1801,7 +1801,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G19" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G20" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G21" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G22" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G23" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G24" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G25" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G26" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>5.521495502500717</v>
       </c>
       <c r="G27" t="n">
-        <v>3.011860975600977</v>
+        <v>2.943761256716523</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>5.521495502500717</v>
       </c>
       <c r="G28" t="n">
-        <v>3.011860975600977</v>
+        <v>2.943761256716523</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>4.997676066482427</v>
       </c>
       <c r="G29" t="n">
-        <v>3.011860975600977</v>
+        <v>2.943761256716523</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
@@ -2164,7 +2164,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G30" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G31" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G32" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G33" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G34" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G35" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G36" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G37" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G38" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G39" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G40" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G41" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G42" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>6.762441551542405</v>
       </c>
       <c r="G43" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>6.690735213210944</v>
       </c>
       <c r="G44" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>6.690735213210944</v>
       </c>
       <c r="G45" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>6.690735213210944</v>
       </c>
       <c r="G46" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>6.690735213210944</v>
       </c>
       <c r="G47" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>6.690735213210944</v>
       </c>
       <c r="G48" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G49" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G50" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G51" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G52" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G53" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G54" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G55" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G56" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G57" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>6.472156620777877</v>
       </c>
       <c r="G58" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3118,18 +3118,18 @@
         <v>2.357996053434613</v>
       </c>
       <c r="F59" t="n">
-        <v>4.760992934867661</v>
+        <v>5.894329590125656</v>
       </c>
       <c r="G59" t="n">
-        <v>4.760992934867661</v>
+        <v>5.788625016942598</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
@@ -3154,7 +3154,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G60" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G61" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G62" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G63" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G64" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G65" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G66" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G67" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G68" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G69" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G70" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G71" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>5.020426923325401</v>
       </c>
       <c r="G72" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>4.895600538268938</v>
       </c>
       <c r="G73" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>791</v>
+        <v>835</v>
       </c>
     </row>
     <row r="74">
@@ -3781,7 +3781,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G79" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G80" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G81" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G82" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G83" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G84" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G85" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G86" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G87" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>5.574854912670763</v>
       </c>
       <c r="G88" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4108,10 +4108,10 @@
         <v>0.6730859682431891</v>
       </c>
       <c r="F89" t="n">
-        <v>4.901768944427574</v>
+        <v>4.99358678609173</v>
       </c>
       <c r="G89" t="n">
-        <v>4.350165419671936</v>
+        <v>4.654181845634831</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
@@ -4144,7 +4144,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="G90" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="G91" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>8.477002814113927</v>
       </c>
       <c r="G92" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>8.477002814113927</v>
       </c>
       <c r="G93" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>4.82906977588766</v>
       </c>
       <c r="G94" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1913</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="95">
@@ -4573,7 +4573,7 @@
         <v>7.506210694773125</v>
       </c>
       <c r="G103" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G104" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G105" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G106" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G107" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G108" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G109" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G110" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>5.254309458726135</v>
       </c>
       <c r="G111" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>5.191560242752534</v>
       </c>
       <c r="G112" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>5.191560242752534</v>
       </c>
       <c r="G113" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>5.191560242752534</v>
       </c>
       <c r="G114" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>5.128778960398204</v>
       </c>
       <c r="G115" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>4.993770254566507</v>
       </c>
       <c r="G116" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1044</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="117">
@@ -5035,7 +5035,7 @@
         <v>6.728028039408759</v>
       </c>
       <c r="G117" t="n">
-        <v>1.282884978605355</v>
+        <v>1.139081242331629</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>4.795975135162163</v>
       </c>
       <c r="G118" t="n">
-        <v>1.282884978605355</v>
+        <v>1.139081242331629</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2315</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="119">
@@ -5794,7 +5794,7 @@
         <v>8.274118065635113</v>
       </c>
       <c r="G140" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>8.274118065635113</v>
       </c>
       <c r="G141" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>8.274118065635113</v>
       </c>
       <c r="G142" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>8.274118065635113</v>
       </c>
       <c r="G143" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>5.138458324574408</v>
       </c>
       <c r="G144" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>4.960258441140554</v>
       </c>
       <c r="G145" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="146">
@@ -6025,7 +6025,7 @@
         <v>8.337791569994524</v>
       </c>
       <c r="G147" t="n">
-        <v>5.548733388209437</v>
+        <v>4.654967477232781</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6039,34 +6039,34 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ROKU US Equity</t>
+          <t>RBLX US Equity</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>43915</v>
+        <v>45936</v>
       </c>
       <c r="C148" t="n">
-        <v>5.244790560642596</v>
+        <v>8.337791569994524</v>
       </c>
       <c r="D148" t="n">
-        <v>4.877677857849529</v>
+        <v>4.693697736216864</v>
       </c>
       <c r="E148" t="n">
-        <v>0.367112702793067</v>
+        <v>3.64409383377766</v>
       </c>
       <c r="F148" t="n">
-        <v>11.37479646261744</v>
+        <v>4.738498273771739</v>
       </c>
       <c r="G148" t="n">
-        <v>6.859793191005789</v>
+        <v>4.654967477232781</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
@@ -6076,22 +6076,22 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>43948</v>
+        <v>43915</v>
       </c>
       <c r="C149" t="n">
-        <v>5.694997239609114</v>
+        <v>5.244790560642596</v>
       </c>
       <c r="D149" t="n">
-        <v>4.92595473598861</v>
+        <v>4.877677857849529</v>
       </c>
       <c r="E149" t="n">
-        <v>0.7690425036205033</v>
+        <v>0.367112702793067</v>
       </c>
       <c r="F149" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G149" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150">
@@ -6109,22 +6109,22 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>43959</v>
+        <v>43948</v>
       </c>
       <c r="C150" t="n">
         <v>5.694997239609114</v>
       </c>
       <c r="D150" t="n">
-        <v>4.633809446880876</v>
+        <v>4.92595473598861</v>
       </c>
       <c r="E150" t="n">
-        <v>1.061187792728238</v>
+        <v>0.7690425036205033</v>
       </c>
       <c r="F150" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G150" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151">
@@ -6142,22 +6142,22 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>43963</v>
+        <v>43959</v>
       </c>
       <c r="C151" t="n">
         <v>5.694997239609114</v>
       </c>
       <c r="D151" t="n">
-        <v>4.953313661977649</v>
+        <v>4.633809446880876</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7416835776314645</v>
+        <v>1.061187792728238</v>
       </c>
       <c r="F151" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G151" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -6175,22 +6175,22 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>43992</v>
+        <v>43963</v>
       </c>
       <c r="C152" t="n">
         <v>5.694997239609114</v>
       </c>
       <c r="D152" t="n">
-        <v>4.976648256367</v>
+        <v>4.953313661977649</v>
       </c>
       <c r="E152" t="n">
-        <v>0.7183489832421133</v>
+        <v>0.7416835776314645</v>
       </c>
       <c r="F152" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G152" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="153">
@@ -6208,22 +6208,22 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>43997</v>
+        <v>43992</v>
       </c>
       <c r="C153" t="n">
         <v>5.694997239609114</v>
       </c>
       <c r="D153" t="n">
-        <v>4.836458823714893</v>
+        <v>4.976648256367</v>
       </c>
       <c r="E153" t="n">
-        <v>0.8585384158942206</v>
+        <v>0.7183489832421133</v>
       </c>
       <c r="F153" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G153" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6241,22 +6241,22 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>44054</v>
+        <v>43997</v>
       </c>
       <c r="C154" t="n">
-        <v>6.225492200180911</v>
+        <v>5.694997239609114</v>
       </c>
       <c r="D154" t="n">
-        <v>4.99073995363005</v>
+        <v>4.836458823714893</v>
       </c>
       <c r="E154" t="n">
-        <v>1.234752246550861</v>
+        <v>0.8585384158942206</v>
       </c>
       <c r="F154" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G154" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -6274,22 +6274,22 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>44070</v>
+        <v>44054</v>
       </c>
       <c r="C155" t="n">
         <v>6.225492200180911</v>
       </c>
       <c r="D155" t="n">
-        <v>4.940119154189013</v>
+        <v>4.99073995363005</v>
       </c>
       <c r="E155" t="n">
-        <v>1.285373045991898</v>
+        <v>1.234752246550861</v>
       </c>
       <c r="F155" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G155" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156">
@@ -6307,22 +6307,22 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>44083</v>
+        <v>44070</v>
       </c>
       <c r="C156" t="n">
         <v>6.225492200180911</v>
       </c>
       <c r="D156" t="n">
-        <v>4.942532613000529</v>
+        <v>4.940119154189013</v>
       </c>
       <c r="E156" t="n">
-        <v>1.282959587180382</v>
+        <v>1.285373045991898</v>
       </c>
       <c r="F156" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G156" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>44316</v>
+        <v>44083</v>
       </c>
       <c r="C157" t="n">
-        <v>7.69087110314066</v>
+        <v>6.225492200180911</v>
       </c>
       <c r="D157" t="n">
-        <v>4.997100159829337</v>
+        <v>4.942532613000529</v>
       </c>
       <c r="E157" t="n">
-        <v>2.693770943311323</v>
+        <v>1.282959587180382</v>
       </c>
       <c r="F157" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G157" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158">
@@ -6373,22 +6373,22 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>44320</v>
+        <v>44316</v>
       </c>
       <c r="C158" t="n">
         <v>7.69087110314066</v>
       </c>
       <c r="D158" t="n">
-        <v>4.968320800153019</v>
+        <v>4.997100159829337</v>
       </c>
       <c r="E158" t="n">
-        <v>2.722550302987641</v>
+        <v>2.693770943311323</v>
       </c>
       <c r="F158" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G158" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6406,22 +6406,22 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>44441</v>
+        <v>44320</v>
       </c>
       <c r="C159" t="n">
         <v>7.69087110314066</v>
       </c>
       <c r="D159" t="n">
-        <v>4.985615603797091</v>
+        <v>4.968320800153019</v>
       </c>
       <c r="E159" t="n">
-        <v>2.705255499343569</v>
+        <v>2.722550302987641</v>
       </c>
       <c r="F159" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G159" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -6439,22 +6439,22 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>44456</v>
+        <v>44441</v>
       </c>
       <c r="C160" t="n">
         <v>7.69087110314066</v>
       </c>
       <c r="D160" t="n">
-        <v>4.94166653989855</v>
+        <v>4.985615603797091</v>
       </c>
       <c r="E160" t="n">
-        <v>2.74920456324211</v>
+        <v>2.705255499343569</v>
       </c>
       <c r="F160" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G160" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
@@ -6472,22 +6472,22 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>44505</v>
+        <v>44456</v>
       </c>
       <c r="C161" t="n">
         <v>7.69087110314066</v>
       </c>
       <c r="D161" t="n">
-        <v>4.973378674888633</v>
+        <v>4.94166653989855</v>
       </c>
       <c r="E161" t="n">
-        <v>2.717492428252027</v>
+        <v>2.74920456324211</v>
       </c>
       <c r="F161" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G161" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -6505,22 +6505,22 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>44509</v>
+        <v>44505</v>
       </c>
       <c r="C162" t="n">
         <v>7.69087110314066</v>
       </c>
       <c r="D162" t="n">
-        <v>4.958927076089591</v>
+        <v>4.973378674888633</v>
       </c>
       <c r="E162" t="n">
-        <v>2.731944027051069</v>
+        <v>2.717492428252027</v>
       </c>
       <c r="F162" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G162" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -6538,22 +6538,22 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>44518</v>
+        <v>44509</v>
       </c>
       <c r="C163" t="n">
         <v>7.69087110314066</v>
       </c>
       <c r="D163" t="n">
-        <v>4.920799646407995</v>
+        <v>4.958927076089591</v>
       </c>
       <c r="E163" t="n">
-        <v>2.770071456732665</v>
+        <v>2.731944027051069</v>
       </c>
       <c r="F163" t="n">
         <v>11.37479646261744</v>
       </c>
       <c r="G163" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -6561,32 +6561,32 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SHOP CN Equity</t>
+          <t>ROKU US Equity</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>44403</v>
+        <v>44518</v>
       </c>
       <c r="C164" t="n">
-        <v>5.076691819189668</v>
+        <v>7.69087110314066</v>
       </c>
       <c r="D164" t="n">
-        <v>4.933586298027473</v>
+        <v>4.920799646407995</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1431055211621954</v>
+        <v>2.770071456732665</v>
       </c>
       <c r="F164" t="n">
-        <v>22.94611580904625</v>
+        <v>11.37479646261744</v>
       </c>
       <c r="G164" t="n">
-        <v>4.9920031732234</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>338</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
@@ -6604,22 +6604,22 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>44742</v>
+        <v>44403</v>
       </c>
       <c r="C165" t="n">
+        <v>5.076691819189668</v>
+      </c>
+      <c r="D165" t="n">
+        <v>4.933586298027473</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.1431055211621954</v>
+      </c>
+      <c r="F165" t="n">
         <v>22.94611580904625</v>
       </c>
-      <c r="D165" t="n">
-        <v>2.772578164399191</v>
-      </c>
-      <c r="E165" t="n">
-        <v>20.17353764464706</v>
-      </c>
-      <c r="F165" t="n">
-        <v>5.918939785920623</v>
-      </c>
       <c r="G165" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>188</v>
+        <v>338</v>
       </c>
     </row>
     <row r="166">
@@ -6637,22 +6637,22 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>44932</v>
+        <v>44742</v>
       </c>
       <c r="C166" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D166" t="n">
-        <v>4.989864997988601</v>
+        <v>2.772578164399191</v>
       </c>
       <c r="E166" t="n">
-        <v>17.95625081105765</v>
+        <v>20.17353764464706</v>
       </c>
       <c r="F166" t="n">
         <v>5.918939785920623</v>
       </c>
       <c r="G166" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
     </row>
     <row r="167">
@@ -6670,22 +6670,22 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>44936</v>
+        <v>44932</v>
       </c>
       <c r="C167" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D167" t="n">
-        <v>4.876702759073809</v>
+        <v>4.989864997988601</v>
       </c>
       <c r="E167" t="n">
-        <v>18.06941304997244</v>
+        <v>17.95625081105765</v>
       </c>
       <c r="F167" t="n">
         <v>5.918939785920623</v>
       </c>
       <c r="G167" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -6703,22 +6703,22 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>44974</v>
+        <v>44936</v>
       </c>
       <c r="C168" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D168" t="n">
-        <v>4.93149529579162</v>
+        <v>4.876702759073809</v>
       </c>
       <c r="E168" t="n">
-        <v>18.01462051325463</v>
+        <v>18.06941304997244</v>
       </c>
       <c r="F168" t="n">
         <v>5.918939785920623</v>
       </c>
       <c r="G168" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169">
@@ -6736,22 +6736,22 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>44984</v>
+        <v>44974</v>
       </c>
       <c r="C169" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D169" t="n">
-        <v>4.960117016111814</v>
+        <v>4.93149529579162</v>
       </c>
       <c r="E169" t="n">
-        <v>17.98599879293444</v>
+        <v>18.01462051325463</v>
       </c>
       <c r="F169" t="n">
         <v>5.918939785920623</v>
       </c>
       <c r="G169" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -6769,22 +6769,22 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>45044</v>
+        <v>44984</v>
       </c>
       <c r="C170" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D170" t="n">
-        <v>4.920709499946115</v>
+        <v>4.960117016111814</v>
       </c>
       <c r="E170" t="n">
-        <v>18.02540630910013</v>
+        <v>17.98599879293444</v>
       </c>
       <c r="F170" t="n">
-        <v>5.870941234736309</v>
+        <v>5.918939785920623</v>
       </c>
       <c r="G170" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -6802,22 +6802,22 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>45070</v>
+        <v>45044</v>
       </c>
       <c r="C171" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D171" t="n">
-        <v>4.797670870831372</v>
+        <v>4.920709499946115</v>
       </c>
       <c r="E171" t="n">
-        <v>18.14844493821488</v>
+        <v>18.02540630910013</v>
       </c>
       <c r="F171" t="n">
         <v>5.870941234736309</v>
       </c>
       <c r="G171" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>720</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -6835,22 +6835,22 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>45791</v>
+        <v>45070</v>
       </c>
       <c r="C172" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D172" t="n">
-        <v>4.940109846343597</v>
+        <v>4.797670870831372</v>
       </c>
       <c r="E172" t="n">
-        <v>18.00600596270266</v>
+        <v>18.14844493821488</v>
       </c>
       <c r="F172" t="n">
         <v>5.870941234736309</v>
       </c>
       <c r="G172" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>720</v>
       </c>
     </row>
     <row r="173">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>45797</v>
+        <v>45791</v>
       </c>
       <c r="C173" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D173" t="n">
-        <v>4.991488711425601</v>
+        <v>4.940109846343597</v>
       </c>
       <c r="E173" t="n">
-        <v>17.95462709762065</v>
+        <v>18.00600596270266</v>
       </c>
       <c r="F173" t="n">
         <v>5.870941234736309</v>
       </c>
       <c r="G173" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -6901,22 +6901,22 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>45811</v>
+        <v>45797</v>
       </c>
       <c r="C174" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D174" t="n">
-        <v>4.898614949306794</v>
+        <v>4.991488711425601</v>
       </c>
       <c r="E174" t="n">
-        <v>18.04750085973946</v>
+        <v>17.95462709762065</v>
       </c>
       <c r="F174" t="n">
         <v>5.870941234736309</v>
       </c>
       <c r="G174" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175">
@@ -6934,22 +6934,22 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>45884</v>
+        <v>45811</v>
       </c>
       <c r="C175" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D175" t="n">
-        <v>4.980561674055635</v>
+        <v>4.898614949306794</v>
       </c>
       <c r="E175" t="n">
-        <v>17.96555413499062</v>
+        <v>18.04750085973946</v>
       </c>
       <c r="F175" t="n">
-        <v>5.032628036870259</v>
+        <v>5.870941234736309</v>
       </c>
       <c r="G175" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="176">
@@ -6967,55 +6967,55 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>45896</v>
+        <v>45884</v>
       </c>
       <c r="C176" t="n">
         <v>22.94611580904625</v>
       </c>
       <c r="D176" t="n">
-        <v>4.9920031732234</v>
+        <v>4.980561674055635</v>
       </c>
       <c r="E176" t="n">
-        <v>17.95411263582285</v>
+        <v>17.96555413499062</v>
       </c>
       <c r="F176" t="n">
-        <v>4.9920031732234</v>
+        <v>5.263736871021505</v>
       </c>
       <c r="G176" t="n">
-        <v>4.9920031732234</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SSYS US Equity</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>42060</v>
+        <v>45896</v>
       </c>
       <c r="C177" t="n">
-        <v>5.078822192324484</v>
+        <v>22.94611580904625</v>
       </c>
       <c r="D177" t="n">
-        <v>4.95479127077567</v>
+        <v>4.9920031732234</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1240309215488145</v>
+        <v>17.95411263582285</v>
       </c>
       <c r="F177" t="n">
-        <v>9.25657686422101</v>
+        <v>5.263736871021505</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7023,32 +7023,32 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SSYS US Equity</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>42066</v>
+        <v>45915</v>
       </c>
       <c r="C178" t="n">
-        <v>5.078822192324484</v>
+        <v>22.94611580904625</v>
       </c>
       <c r="D178" t="n">
-        <v>4.989576459823126</v>
+        <v>4.946400178425749</v>
       </c>
       <c r="E178" t="n">
-        <v>0.08924573250135825</v>
+        <v>17.9997156306205</v>
       </c>
       <c r="F178" t="n">
-        <v>9.25657686422101</v>
+        <v>5.033455094871471</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7062,26 +7062,26 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SSYS US Equity</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>42079</v>
+        <v>45917</v>
       </c>
       <c r="C179" t="n">
-        <v>5.184412307404881</v>
+        <v>22.94611580904625</v>
       </c>
       <c r="D179" t="n">
-        <v>4.773771191903039</v>
+        <v>4.914641738785458</v>
       </c>
       <c r="E179" t="n">
-        <v>0.4106411155018419</v>
+        <v>18.03147407026079</v>
       </c>
       <c r="F179" t="n">
-        <v>9.25657686422101</v>
+        <v>5.033455094871471</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7089,40 +7089,40 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SSYS US Equity</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>42115</v>
+        <v>45924</v>
       </c>
       <c r="C180" t="n">
-        <v>5.527871077559317</v>
+        <v>22.94611580904625</v>
       </c>
       <c r="D180" t="n">
-        <v>4.827091820660856</v>
+        <v>4.853789526471231</v>
       </c>
       <c r="E180" t="n">
-        <v>0.7007792568984605</v>
+        <v>18.09232628257502</v>
       </c>
       <c r="F180" t="n">
-        <v>9.25657686422101</v>
+        <v>4.973473965106376</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>4.867609752572441</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181">
@@ -7132,16 +7132,16 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>42123</v>
+        <v>42060</v>
       </c>
       <c r="C181" t="n">
-        <v>5.527871077559317</v>
+        <v>5.078822192324484</v>
       </c>
       <c r="D181" t="n">
-        <v>4.183211968028874</v>
+        <v>4.95479127077567</v>
       </c>
       <c r="E181" t="n">
-        <v>1.344659109530443</v>
+        <v>0.1240309215488145</v>
       </c>
       <c r="F181" t="n">
         <v>9.25657686422101</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182">
@@ -7165,19 +7165,19 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>42912</v>
+        <v>42066</v>
       </c>
       <c r="C182" t="n">
+        <v>5.078822192324484</v>
+      </c>
+      <c r="D182" t="n">
+        <v>4.989576459823126</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.08924573250135825</v>
+      </c>
+      <c r="F182" t="n">
         <v>9.25657686422101</v>
-      </c>
-      <c r="D182" t="n">
-        <v>4.500905650417555</v>
-      </c>
-      <c r="E182" t="n">
-        <v>4.755671213803455</v>
-      </c>
-      <c r="F182" t="n">
-        <v>8.179615649716796</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -7198,19 +7198,19 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>43054</v>
+        <v>42079</v>
       </c>
       <c r="C183" t="n">
+        <v>5.184412307404881</v>
+      </c>
+      <c r="D183" t="n">
+        <v>4.773771191903039</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.4106411155018419</v>
+      </c>
+      <c r="F183" t="n">
         <v>9.25657686422101</v>
-      </c>
-      <c r="D183" t="n">
-        <v>4.862058862499706</v>
-      </c>
-      <c r="E183" t="n">
-        <v>4.394518001721305</v>
-      </c>
-      <c r="F183" t="n">
-        <v>8.179615649716796</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="184">
@@ -7231,19 +7231,19 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>43061</v>
+        <v>42115</v>
       </c>
       <c r="C184" t="n">
+        <v>5.527871077559317</v>
+      </c>
+      <c r="D184" t="n">
+        <v>4.827091820660856</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.7007792568984605</v>
+      </c>
+      <c r="F184" t="n">
         <v>9.25657686422101</v>
-      </c>
-      <c r="D184" t="n">
-        <v>4.985681597700826</v>
-      </c>
-      <c r="E184" t="n">
-        <v>4.270895266520184</v>
-      </c>
-      <c r="F184" t="n">
-        <v>8.179615649716796</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -7264,19 +7264,19 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>43066</v>
+        <v>42123</v>
       </c>
       <c r="C185" t="n">
+        <v>5.527871077559317</v>
+      </c>
+      <c r="D185" t="n">
+        <v>4.183211968028874</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.344659109530443</v>
+      </c>
+      <c r="F185" t="n">
         <v>9.25657686422101</v>
-      </c>
-      <c r="D185" t="n">
-        <v>4.974175389028916</v>
-      </c>
-      <c r="E185" t="n">
-        <v>4.282401475192094</v>
-      </c>
-      <c r="F185" t="n">
-        <v>8.179615649716796</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -7297,16 +7297,16 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>43087</v>
+        <v>42912</v>
       </c>
       <c r="C186" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D186" t="n">
-        <v>4.817624446941378</v>
+        <v>4.500905650417555</v>
       </c>
       <c r="E186" t="n">
-        <v>4.438952417279633</v>
+        <v>4.755671213803455</v>
       </c>
       <c r="F186" t="n">
         <v>8.179615649716796</v>
@@ -7320,7 +7320,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>24</v>
+        <v>141</v>
       </c>
     </row>
     <row r="187">
@@ -7330,16 +7330,16 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>43159</v>
+        <v>43054</v>
       </c>
       <c r="C187" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D187" t="n">
-        <v>4.693473702176282</v>
+        <v>4.862058862499706</v>
       </c>
       <c r="E187" t="n">
-        <v>4.563103162044729</v>
+        <v>4.394518001721305</v>
       </c>
       <c r="F187" t="n">
         <v>8.179615649716796</v>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
@@ -7363,19 +7363,19 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>43865</v>
+        <v>43061</v>
       </c>
       <c r="C188" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D188" t="n">
-        <v>4.938103403036679</v>
+        <v>4.985681597700826</v>
       </c>
       <c r="E188" t="n">
-        <v>4.318473461184332</v>
+        <v>4.270895266520184</v>
       </c>
       <c r="F188" t="n">
-        <v>6.542496445927439</v>
+        <v>8.179615649716796</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -7396,19 +7396,19 @@
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>43867</v>
+        <v>43066</v>
       </c>
       <c r="C189" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D189" t="n">
-        <v>4.881877285783112</v>
+        <v>4.974175389028916</v>
       </c>
       <c r="E189" t="n">
-        <v>4.374699578437898</v>
+        <v>4.282401475192094</v>
       </c>
       <c r="F189" t="n">
-        <v>6.542496445927439</v>
+        <v>8.179615649716796</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190">
@@ -7429,19 +7429,19 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>43875</v>
+        <v>43087</v>
       </c>
       <c r="C190" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D190" t="n">
-        <v>4.867933960789055</v>
+        <v>4.817624446941378</v>
       </c>
       <c r="E190" t="n">
-        <v>4.388642903431955</v>
+        <v>4.438952417279633</v>
       </c>
       <c r="F190" t="n">
-        <v>6.542496445927439</v>
+        <v>8.179615649716796</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="191">
@@ -7462,19 +7462,19 @@
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>43924</v>
+        <v>43159</v>
       </c>
       <c r="C191" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D191" t="n">
-        <v>4.963361986572595</v>
+        <v>4.693473702176282</v>
       </c>
       <c r="E191" t="n">
-        <v>4.293214877648415</v>
+        <v>4.563103162044729</v>
       </c>
       <c r="F191" t="n">
-        <v>5.239952449745958</v>
+        <v>8.179615649716796</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -7495,19 +7495,19 @@
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>43928</v>
+        <v>43865</v>
       </c>
       <c r="C192" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D192" t="n">
-        <v>4.841240507354375</v>
+        <v>4.938103403036679</v>
       </c>
       <c r="E192" t="n">
-        <v>4.415336356866635</v>
+        <v>4.318473461184332</v>
       </c>
       <c r="F192" t="n">
-        <v>5.084952013037499</v>
+        <v>6.542496445927439</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -7528,85 +7528,85 @@
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>43934</v>
+        <v>43867</v>
       </c>
       <c r="C193" t="n">
         <v>9.25657686422101</v>
       </c>
       <c r="D193" t="n">
-        <v>4.862802475225053</v>
+        <v>4.881877285783112</v>
       </c>
       <c r="E193" t="n">
-        <v>4.393774388995957</v>
+        <v>4.374699578437898</v>
       </c>
       <c r="F193" t="n">
-        <v>4.958929882606012</v>
+        <v>6.542496445927439</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>827</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TCEHY US Equity</t>
+          <t>SSYS US Equity</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>43458</v>
+        <v>43875</v>
       </c>
       <c r="C194" t="n">
-        <v>5.253022851403059</v>
+        <v>9.25657686422101</v>
       </c>
       <c r="D194" t="n">
-        <v>4.97555800960592</v>
+        <v>4.867933960789055</v>
       </c>
       <c r="E194" t="n">
-        <v>0.2774648417971388</v>
+        <v>4.388642903431955</v>
       </c>
       <c r="F194" t="n">
-        <v>4.97555800960592</v>
+        <v>6.542496445927439</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>942</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>SSYS US Equity</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>44229</v>
+        <v>43924</v>
       </c>
       <c r="C195" t="n">
-        <v>5.507930065638074</v>
+        <v>9.25657686422101</v>
       </c>
       <c r="D195" t="n">
-        <v>4.978425533527024</v>
+        <v>4.963361986572595</v>
       </c>
       <c r="E195" t="n">
-        <v>0.5295045321110496</v>
+        <v>4.293214877648415</v>
       </c>
       <c r="F195" t="n">
-        <v>7.115410569568524</v>
+        <v>5.239952449745958</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -7617,29 +7617,29 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>SSYS US Equity</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>44252</v>
+        <v>43928</v>
       </c>
       <c r="C196" t="n">
-        <v>5.507930065638074</v>
+        <v>9.25657686422101</v>
       </c>
       <c r="D196" t="n">
-        <v>4.62445041525013</v>
+        <v>4.841240507354375</v>
       </c>
       <c r="E196" t="n">
-        <v>0.8834796503879438</v>
+        <v>4.415336356866635</v>
       </c>
       <c r="F196" t="n">
-        <v>7.115410569568524</v>
+        <v>5.084952013037499</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -7650,62 +7650,62 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>SSYS US Equity</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>44680</v>
+        <v>43934</v>
       </c>
       <c r="C197" t="n">
-        <v>7.115410569568524</v>
+        <v>9.25657686422101</v>
       </c>
       <c r="D197" t="n">
-        <v>4.278467925749932</v>
+        <v>4.862802475225053</v>
       </c>
       <c r="E197" t="n">
-        <v>2.836942643818592</v>
+        <v>4.393774388995957</v>
       </c>
       <c r="F197" t="n">
-        <v>5.244168808399899</v>
+        <v>4.958929882606012</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>70</v>
+        <v>827</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>TCEHY US Equity</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>44771</v>
+        <v>43458</v>
       </c>
       <c r="C198" t="n">
-        <v>7.115410569568524</v>
+        <v>5.253022851403059</v>
       </c>
       <c r="D198" t="n">
-        <v>4.444535939562408</v>
+        <v>4.97555800960592</v>
       </c>
       <c r="E198" t="n">
-        <v>2.670874630006116</v>
+        <v>0.2774648417971388</v>
       </c>
       <c r="F198" t="n">
-        <v>4.832269293142117</v>
+        <v>4.97555800960592</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -7716,32 +7716,32 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>761</v>
+        <v>942</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TEM US Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>45707</v>
+        <v>44229</v>
       </c>
       <c r="C199" t="n">
-        <v>5.267988380058403</v>
+        <v>5.507930065638074</v>
       </c>
       <c r="D199" t="n">
-        <v>4.861831477360468</v>
+        <v>4.978425533527024</v>
       </c>
       <c r="E199" t="n">
-        <v>0.4061569026979353</v>
+        <v>0.5295045321110496</v>
       </c>
       <c r="F199" t="n">
-        <v>6.460707351114836</v>
+        <v>7.115410569568524</v>
       </c>
       <c r="G199" t="n">
-        <v>5.495887774411774</v>
+        <v>0</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -7755,26 +7755,26 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TEM US Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>45709</v>
+        <v>44252</v>
       </c>
       <c r="C200" t="n">
-        <v>5.267988380058403</v>
+        <v>5.507930065638074</v>
       </c>
       <c r="D200" t="n">
-        <v>4.726640645951312</v>
+        <v>4.62445041525013</v>
       </c>
       <c r="E200" t="n">
-        <v>0.5413477341070916</v>
+        <v>0.8834796503879438</v>
       </c>
       <c r="F200" t="n">
-        <v>6.460707351114836</v>
+        <v>7.115410569568524</v>
       </c>
       <c r="G200" t="n">
-        <v>5.495887774411774</v>
+        <v>0</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -7782,32 +7782,32 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TEM US Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>45747</v>
+        <v>44680</v>
       </c>
       <c r="C201" t="n">
-        <v>5.36392153885542</v>
+        <v>7.115410569568524</v>
       </c>
       <c r="D201" t="n">
-        <v>4.84307315968205</v>
+        <v>4.278467925749932</v>
       </c>
       <c r="E201" t="n">
-        <v>0.52084837917337</v>
+        <v>2.836942643818592</v>
       </c>
       <c r="F201" t="n">
-        <v>6.460707351114836</v>
+        <v>5.244168808399899</v>
       </c>
       <c r="G201" t="n">
-        <v>5.495887774411774</v>
+        <v>0</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -7815,40 +7815,40 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TEM US Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>45749</v>
+        <v>44771</v>
       </c>
       <c r="C202" t="n">
-        <v>5.36392153885542</v>
+        <v>7.115410569568524</v>
       </c>
       <c r="D202" t="n">
-        <v>4.869234181720903</v>
+        <v>4.444535939562408</v>
       </c>
       <c r="E202" t="n">
-        <v>0.4946873571345174</v>
+        <v>2.670874630006116</v>
       </c>
       <c r="F202" t="n">
-        <v>6.460707351114836</v>
+        <v>4.832269293142117</v>
       </c>
       <c r="G202" t="n">
-        <v>5.495887774411774</v>
+        <v>0</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>761</v>
       </c>
     </row>
     <row r="203">
@@ -7858,22 +7858,22 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>45755</v>
+        <v>45707</v>
       </c>
       <c r="C203" t="n">
-        <v>5.36392153885542</v>
+        <v>5.267988380058403</v>
       </c>
       <c r="D203" t="n">
-        <v>4.996196020862222</v>
+        <v>4.861831477360468</v>
       </c>
       <c r="E203" t="n">
-        <v>0.3677255179931977</v>
+        <v>0.4061569026979353</v>
       </c>
       <c r="F203" t="n">
         <v>6.460707351114836</v>
       </c>
       <c r="G203" t="n">
-        <v>5.495887774411774</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -7891,22 +7891,22 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>45806</v>
+        <v>45709</v>
       </c>
       <c r="C204" t="n">
+        <v>5.267988380058403</v>
+      </c>
+      <c r="D204" t="n">
+        <v>4.726640645951312</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0.5413477341070916</v>
+      </c>
+      <c r="F204" t="n">
         <v>6.460707351114836</v>
       </c>
-      <c r="D204" t="n">
-        <v>4.955908721354735</v>
-      </c>
-      <c r="E204" t="n">
-        <v>1.504798629760101</v>
-      </c>
-      <c r="F204" t="n">
-        <v>6.09560211267607</v>
-      </c>
       <c r="G204" t="n">
-        <v>5.495887774411774</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="205">
@@ -7924,22 +7924,22 @@
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>45839</v>
+        <v>45747</v>
       </c>
       <c r="C205" t="n">
+        <v>5.36392153885542</v>
+      </c>
+      <c r="D205" t="n">
+        <v>4.84307315968205</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.52084837917337</v>
+      </c>
+      <c r="F205" t="n">
         <v>6.460707351114836</v>
       </c>
-      <c r="D205" t="n">
-        <v>4.79603274227745</v>
-      </c>
-      <c r="E205" t="n">
-        <v>1.664674608837386</v>
-      </c>
-      <c r="F205" t="n">
-        <v>5.776512677192605</v>
-      </c>
       <c r="G205" t="n">
-        <v>5.495887774411774</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -7947,32 +7947,32 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TSLA US Equity</t>
+          <t>TEM US Equity</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>42164</v>
+        <v>45749</v>
       </c>
       <c r="C206" t="n">
-        <v>8.007379230835186</v>
+        <v>5.36392153885542</v>
       </c>
       <c r="D206" t="n">
-        <v>4.996953284544655</v>
+        <v>4.869234181720903</v>
       </c>
       <c r="E206" t="n">
-        <v>3.010425946290531</v>
+        <v>0.4946873571345174</v>
       </c>
       <c r="F206" t="n">
-        <v>25.15214959020717</v>
+        <v>6.460707351114836</v>
       </c>
       <c r="G206" t="n">
-        <v>11.05528643740157</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -7980,32 +7980,32 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TSLA US Equity</t>
+          <t>TEM US Equity</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>42177</v>
+        <v>45755</v>
       </c>
       <c r="C207" t="n">
-        <v>8.007379230835186</v>
+        <v>5.36392153885542</v>
       </c>
       <c r="D207" t="n">
-        <v>4.958296491018094</v>
+        <v>4.996196020862222</v>
       </c>
       <c r="E207" t="n">
-        <v>3.049082739817092</v>
+        <v>0.3677255179931977</v>
       </c>
       <c r="F207" t="n">
-        <v>25.15214959020717</v>
+        <v>6.460707351114836</v>
       </c>
       <c r="G207" t="n">
-        <v>11.05528643740157</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8013,32 +8013,32 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TSLA US Equity</t>
+          <t>TEM US Equity</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>42192</v>
+        <v>45806</v>
       </c>
       <c r="C208" t="n">
-        <v>8.007379230835186</v>
+        <v>6.460707351114836</v>
       </c>
       <c r="D208" t="n">
-        <v>4.62836112196742</v>
+        <v>4.955908721354735</v>
       </c>
       <c r="E208" t="n">
-        <v>3.379018108867766</v>
+        <v>1.504798629760101</v>
       </c>
       <c r="F208" t="n">
-        <v>25.15214959020717</v>
+        <v>6.164286263527959</v>
       </c>
       <c r="G208" t="n">
-        <v>11.05528643740157</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8046,32 +8046,32 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TSLA US Equity</t>
+          <t>TEM US Equity</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>42261</v>
+        <v>45839</v>
       </c>
       <c r="C209" t="n">
-        <v>8.007379230835186</v>
+        <v>6.460707351114836</v>
       </c>
       <c r="D209" t="n">
-        <v>4.946961626399887</v>
+        <v>4.79603274227745</v>
       </c>
       <c r="E209" t="n">
-        <v>3.060417604435298</v>
+        <v>1.664674608837386</v>
       </c>
       <c r="F209" t="n">
-        <v>25.15214959020717</v>
+        <v>6.164286263527959</v>
       </c>
       <c r="G209" t="n">
-        <v>11.05528643740157</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -8079,32 +8079,32 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TSLA US Equity</t>
+          <t>TEM US Equity</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>42264</v>
+        <v>45925</v>
       </c>
       <c r="C210" t="n">
-        <v>8.007379230835186</v>
+        <v>6.460707351114836</v>
       </c>
       <c r="D210" t="n">
-        <v>4.995458946693223</v>
+        <v>4.810438396123596</v>
       </c>
       <c r="E210" t="n">
-        <v>3.011920284141963</v>
+        <v>1.65026895499124</v>
       </c>
       <c r="F210" t="n">
-        <v>25.15214959020717</v>
+        <v>5.68116623463181</v>
       </c>
       <c r="G210" t="n">
-        <v>11.05528643740157</v>
+        <v>5.497949280432913</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -8122,22 +8122,22 @@
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>42271</v>
+        <v>42164</v>
       </c>
       <c r="C211" t="n">
         <v>8.007379230835186</v>
       </c>
       <c r="D211" t="n">
-        <v>4.469893898191707</v>
+        <v>4.996953284544655</v>
       </c>
       <c r="E211" t="n">
-        <v>3.537485332643479</v>
+        <v>3.010425946290531</v>
       </c>
       <c r="F211" t="n">
         <v>25.15214959020717</v>
       </c>
       <c r="G211" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
     </row>
     <row r="212">
@@ -8155,22 +8155,22 @@
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>42373</v>
+        <v>42177</v>
       </c>
       <c r="C212" t="n">
         <v>8.007379230835186</v>
       </c>
       <c r="D212" t="n">
-        <v>4.859971965439367</v>
+        <v>4.958296491018094</v>
       </c>
       <c r="E212" t="n">
-        <v>3.147407265395818</v>
+        <v>3.049082739817092</v>
       </c>
       <c r="F212" t="n">
         <v>25.15214959020717</v>
       </c>
       <c r="G212" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -8184,26 +8184,26 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TWOUQ US Equity</t>
+          <t>TSLA US Equity</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>43903</v>
+        <v>42192</v>
       </c>
       <c r="C213" t="n">
-        <v>5.205880349363335</v>
+        <v>8.007379230835186</v>
       </c>
       <c r="D213" t="n">
-        <v>4.806802889264383</v>
+        <v>4.62836112196742</v>
       </c>
       <c r="E213" t="n">
-        <v>0.399077460098952</v>
+        <v>3.379018108867766</v>
       </c>
       <c r="F213" t="n">
-        <v>5.553095715097487</v>
+        <v>25.15214959020717</v>
       </c>
       <c r="G213" t="n">
-        <v>0</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -8211,32 +8211,32 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TWOUQ US Equity</t>
+          <t>TSLA US Equity</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>43963</v>
+        <v>42261</v>
       </c>
       <c r="C214" t="n">
-        <v>5.205880349363335</v>
+        <v>8.007379230835186</v>
       </c>
       <c r="D214" t="n">
-        <v>4.995169161262836</v>
+        <v>4.946961626399887</v>
       </c>
       <c r="E214" t="n">
-        <v>0.2107111881004995</v>
+        <v>3.060417604435298</v>
       </c>
       <c r="F214" t="n">
-        <v>5.553095715097487</v>
+        <v>25.15214959020717</v>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -8244,32 +8244,32 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TWOUQ US Equity</t>
+          <t>TSLA US Equity</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>43978</v>
+        <v>42264</v>
       </c>
       <c r="C215" t="n">
-        <v>5.553095715097487</v>
+        <v>8.007379230835186</v>
       </c>
       <c r="D215" t="n">
-        <v>4.942188014250362</v>
+        <v>4.995458946693223</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6109077008471244</v>
+        <v>3.011920284141963</v>
       </c>
       <c r="F215" t="n">
-        <v>5.122294915383156</v>
+        <v>25.15214959020717</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -8283,59 +8283,59 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TWOUQ US Equity</t>
+          <t>TSLA US Equity</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>43983</v>
+        <v>42271</v>
       </c>
       <c r="C216" t="n">
-        <v>5.553095715097487</v>
+        <v>8.007379230835186</v>
       </c>
       <c r="D216" t="n">
-        <v>4.928428101372063</v>
+        <v>4.469893898191707</v>
       </c>
       <c r="E216" t="n">
-        <v>0.6246676137254239</v>
+        <v>3.537485332643479</v>
       </c>
       <c r="F216" t="n">
-        <v>4.928428101372063</v>
+        <v>25.15214959020717</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1444</v>
+        <v>97</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TSLA US Equity</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>43039</v>
+        <v>42373</v>
       </c>
       <c r="C217" t="n">
-        <v>5.32255249776215</v>
+        <v>8.007379230835186</v>
       </c>
       <c r="D217" t="n">
-        <v>4.980034949039149</v>
+        <v>4.859971965439367</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3425175487230003</v>
+        <v>3.147407265395818</v>
       </c>
       <c r="F217" t="n">
-        <v>5.869132676707429</v>
+        <v>25.15214959020717</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -8349,23 +8349,23 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWOUQ US Equity</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>43041</v>
+        <v>43903</v>
       </c>
       <c r="C218" t="n">
-        <v>5.32255249776215</v>
+        <v>5.205880349363335</v>
       </c>
       <c r="D218" t="n">
-        <v>4.827193065104215</v>
+        <v>4.806802889264383</v>
       </c>
       <c r="E218" t="n">
-        <v>0.4953594326579349</v>
+        <v>0.399077460098952</v>
       </c>
       <c r="F218" t="n">
-        <v>5.869132676707429</v>
+        <v>5.553095715097487</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -8376,29 +8376,29 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWOUQ US Equity</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>43066</v>
+        <v>43963</v>
       </c>
       <c r="C219" t="n">
-        <v>5.32255249776215</v>
+        <v>5.205880349363335</v>
       </c>
       <c r="D219" t="n">
-        <v>4.872194288684964</v>
+        <v>4.995169161262836</v>
       </c>
       <c r="E219" t="n">
-        <v>0.4503582090771854</v>
+        <v>0.2107111881004995</v>
       </c>
       <c r="F219" t="n">
-        <v>5.869132676707429</v>
+        <v>5.553095715097487</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -8409,29 +8409,29 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWOUQ US Equity</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>43102</v>
+        <v>43978</v>
       </c>
       <c r="C220" t="n">
-        <v>5.32255249776215</v>
+        <v>5.553095715097487</v>
       </c>
       <c r="D220" t="n">
-        <v>4.914634024104888</v>
+        <v>4.942188014250362</v>
       </c>
       <c r="E220" t="n">
-        <v>0.4079184736572614</v>
+        <v>0.6109077008471244</v>
       </c>
       <c r="F220" t="n">
-        <v>5.869132676707429</v>
+        <v>5.122294915383156</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -8442,40 +8442,40 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWOUQ US Equity</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>43145</v>
+        <v>43983</v>
       </c>
       <c r="C221" t="n">
-        <v>5.432907846470411</v>
+        <v>5.553095715097487</v>
       </c>
       <c r="D221" t="n">
-        <v>4.851067504648561</v>
+        <v>4.928428101372063</v>
       </c>
       <c r="E221" t="n">
-        <v>0.5818403418218505</v>
+        <v>0.6246676137254239</v>
       </c>
       <c r="F221" t="n">
-        <v>5.869132676707429</v>
+        <v>4.928428101372063</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>107</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="222">
@@ -8485,16 +8485,16 @@
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>43284</v>
+        <v>43039</v>
       </c>
       <c r="C222" t="n">
-        <v>5.462265132323031</v>
+        <v>5.32255249776215</v>
       </c>
       <c r="D222" t="n">
-        <v>4.936747854063999</v>
+        <v>4.980034949039149</v>
       </c>
       <c r="E222" t="n">
-        <v>0.5255172782590325</v>
+        <v>0.3425175487230003</v>
       </c>
       <c r="F222" t="n">
         <v>5.869132676707429</v>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -8518,16 +8518,16 @@
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>43405</v>
+        <v>43041</v>
       </c>
       <c r="C223" t="n">
-        <v>5.462265132323031</v>
+        <v>5.32255249776215</v>
       </c>
       <c r="D223" t="n">
-        <v>4.891916720261024</v>
+        <v>4.827193065104215</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5703484120620068</v>
+        <v>0.4953594326579349</v>
       </c>
       <c r="F223" t="n">
         <v>5.869132676707429</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="224">
@@ -8551,16 +8551,16 @@
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>43451</v>
+        <v>43066</v>
       </c>
       <c r="C224" t="n">
-        <v>5.462265132323031</v>
+        <v>5.32255249776215</v>
       </c>
       <c r="D224" t="n">
-        <v>4.958106572430678</v>
+        <v>4.872194288684964</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5041585598923533</v>
+        <v>0.4503582090771854</v>
       </c>
       <c r="F224" t="n">
         <v>5.869132676707429</v>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="225">
@@ -8584,16 +8584,16 @@
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>43532</v>
+        <v>43102</v>
       </c>
       <c r="C225" t="n">
-        <v>5.462265132323031</v>
+        <v>5.32255249776215</v>
       </c>
       <c r="D225" t="n">
-        <v>4.976041771964095</v>
+        <v>4.914634024104888</v>
       </c>
       <c r="E225" t="n">
-        <v>0.4862233603589363</v>
+        <v>0.4079184736572614</v>
       </c>
       <c r="F225" t="n">
         <v>5.869132676707429</v>
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="226">
@@ -8617,52 +8617,52 @@
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>43588</v>
+        <v>43145</v>
       </c>
       <c r="C226" t="n">
+        <v>5.432907846470411</v>
+      </c>
+      <c r="D226" t="n">
+        <v>4.851067504648561</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.5818403418218505</v>
+      </c>
+      <c r="F226" t="n">
         <v>5.869132676707429</v>
-      </c>
-      <c r="D226" t="n">
-        <v>4.782375534293877</v>
-      </c>
-      <c r="E226" t="n">
-        <v>1.086757142413552</v>
-      </c>
-      <c r="F226" t="n">
-        <v>4.782375534293877</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1021</v>
+        <v>107</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>U US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>44452</v>
+        <v>43284</v>
       </c>
       <c r="C227" t="n">
-        <v>5.083846789178478</v>
+        <v>5.462265132323031</v>
       </c>
       <c r="D227" t="n">
-        <v>4.947092884723148</v>
+        <v>4.936747854063999</v>
       </c>
       <c r="E227" t="n">
-        <v>0.1367539044553308</v>
+        <v>0.5255172782590325</v>
       </c>
       <c r="F227" t="n">
-        <v>6.287573246176271</v>
+        <v>5.869132676707429</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -8673,29 +8673,29 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>U US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>44454</v>
+        <v>43405</v>
       </c>
       <c r="C228" t="n">
-        <v>5.083846789178478</v>
+        <v>5.462265132323031</v>
       </c>
       <c r="D228" t="n">
-        <v>4.998338708772394</v>
+        <v>4.891916720261024</v>
       </c>
       <c r="E228" t="n">
-        <v>0.08550808040608437</v>
+        <v>0.5703484120620068</v>
       </c>
       <c r="F228" t="n">
-        <v>6.287573246176271</v>
+        <v>5.869132676707429</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -8706,29 +8706,29 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>U US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>44459</v>
+        <v>43451</v>
       </c>
       <c r="C229" t="n">
-        <v>5.083846789178478</v>
+        <v>5.462265132323031</v>
       </c>
       <c r="D229" t="n">
-        <v>4.899396956909662</v>
+        <v>4.958106572430678</v>
       </c>
       <c r="E229" t="n">
-        <v>0.1844498322688164</v>
+        <v>0.5041585598923533</v>
       </c>
       <c r="F229" t="n">
-        <v>6.287573246176271</v>
+        <v>5.869132676707429</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -8739,29 +8739,29 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>U US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>44467</v>
+        <v>43532</v>
       </c>
       <c r="C230" t="n">
-        <v>5.321012745945805</v>
+        <v>5.462265132323031</v>
       </c>
       <c r="D230" t="n">
-        <v>4.945956211508276</v>
+        <v>4.976041771964095</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3750565344375287</v>
+        <v>0.4862233603589363</v>
       </c>
       <c r="F230" t="n">
-        <v>6.287573246176271</v>
+        <v>5.869132676707429</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -8772,40 +8772,40 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>U US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>44469</v>
+        <v>43588</v>
       </c>
       <c r="C231" t="n">
-        <v>5.321012745945805</v>
+        <v>5.869132676707429</v>
       </c>
       <c r="D231" t="n">
-        <v>4.989057052662382</v>
+        <v>4.782375534293877</v>
       </c>
       <c r="E231" t="n">
-        <v>0.3319556932834233</v>
+        <v>1.086757142413552</v>
       </c>
       <c r="F231" t="n">
-        <v>6.287573246176271</v>
+        <v>4.782375534293877</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>5</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="232">
@@ -8815,16 +8815,16 @@
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>44502</v>
+        <v>44452</v>
       </c>
       <c r="C232" t="n">
-        <v>5.438857840783777</v>
+        <v>5.083846789178478</v>
       </c>
       <c r="D232" t="n">
-        <v>4.99636274730288</v>
+        <v>4.947092884723148</v>
       </c>
       <c r="E232" t="n">
-        <v>0.4424950934808969</v>
+        <v>0.1367539044553308</v>
       </c>
       <c r="F232" t="n">
         <v>6.287573246176271</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -8848,19 +8848,19 @@
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>44532</v>
+        <v>44454</v>
       </c>
       <c r="C233" t="n">
+        <v>5.083846789178478</v>
+      </c>
+      <c r="D233" t="n">
+        <v>4.998338708772394</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0.08550808040608437</v>
+      </c>
+      <c r="F233" t="n">
         <v>6.287573246176271</v>
-      </c>
-      <c r="D233" t="n">
-        <v>4.851814991185322</v>
-      </c>
-      <c r="E233" t="n">
-        <v>1.435758254990949</v>
-      </c>
-      <c r="F233" t="n">
-        <v>5.089248617513055</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -8881,55 +8881,55 @@
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>44620</v>
+        <v>44459</v>
       </c>
       <c r="C234" t="n">
+        <v>5.083846789178478</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4.899396956909662</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.1844498322688164</v>
+      </c>
+      <c r="F234" t="n">
         <v>6.287573246176271</v>
-      </c>
-      <c r="D234" t="n">
-        <v>4.970008708544596</v>
-      </c>
-      <c r="E234" t="n">
-        <v>1.317564537631675</v>
-      </c>
-      <c r="F234" t="n">
-        <v>4.986763845159937</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I234" t="n">
-        <v>998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>XYZ US Equity</t>
+          <t>U US Equity</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>43494</v>
+        <v>44467</v>
       </c>
       <c r="C235" t="n">
-        <v>6.479343508161802</v>
+        <v>5.321012745945805</v>
       </c>
       <c r="D235" t="n">
-        <v>4.900526077133267</v>
+        <v>4.945956211508276</v>
       </c>
       <c r="E235" t="n">
-        <v>1.578817431028535</v>
+        <v>0.3750565344375287</v>
       </c>
       <c r="F235" t="n">
-        <v>8.981169534111476</v>
+        <v>6.287573246176271</v>
       </c>
       <c r="G235" t="n">
-        <v>1.232373234572589</v>
+        <v>0</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -8943,26 +8943,26 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>XYZ US Equity</t>
+          <t>U US Equity</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>43525</v>
+        <v>44469</v>
       </c>
       <c r="C236" t="n">
-        <v>6.479343508161802</v>
+        <v>5.321012745945805</v>
       </c>
       <c r="D236" t="n">
-        <v>4.98648224894669</v>
+        <v>4.989057052662382</v>
       </c>
       <c r="E236" t="n">
-        <v>1.492861259215111</v>
+        <v>0.3319556932834233</v>
       </c>
       <c r="F236" t="n">
-        <v>8.981169534111476</v>
+        <v>6.287573246176271</v>
       </c>
       <c r="G236" t="n">
-        <v>1.232373234572589</v>
+        <v>0</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -8970,32 +8970,32 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>XYZ US Equity</t>
+          <t>U US Equity</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>43542</v>
+        <v>44502</v>
       </c>
       <c r="C237" t="n">
-        <v>6.479343508161802</v>
+        <v>5.438857840783777</v>
       </c>
       <c r="D237" t="n">
-        <v>4.948813908130575</v>
+        <v>4.99636274730288</v>
       </c>
       <c r="E237" t="n">
-        <v>1.530529600031227</v>
+        <v>0.4424950934808969</v>
       </c>
       <c r="F237" t="n">
-        <v>8.981169534111476</v>
+        <v>6.287573246176271</v>
       </c>
       <c r="G237" t="n">
-        <v>1.232373234572589</v>
+        <v>0</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -9003,32 +9003,32 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>XYZ US Equity</t>
+          <t>U US Equity</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>43544</v>
+        <v>44532</v>
       </c>
       <c r="C238" t="n">
-        <v>6.479343508161802</v>
+        <v>6.287573246176271</v>
       </c>
       <c r="D238" t="n">
-        <v>4.927512009062117</v>
+        <v>4.851814991185322</v>
       </c>
       <c r="E238" t="n">
-        <v>1.551831499099685</v>
+        <v>1.435758254990949</v>
       </c>
       <c r="F238" t="n">
-        <v>8.981169534111476</v>
+        <v>5.089248617513055</v>
       </c>
       <c r="G238" t="n">
-        <v>1.232373234572589</v>
+        <v>0</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -9036,40 +9036,40 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>XYZ US Equity</t>
+          <t>U US Equity</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>43549</v>
+        <v>44620</v>
       </c>
       <c r="C239" t="n">
-        <v>6.479343508161802</v>
+        <v>6.287573246176271</v>
       </c>
       <c r="D239" t="n">
-        <v>4.997154618722668</v>
+        <v>4.970008708544596</v>
       </c>
       <c r="E239" t="n">
-        <v>1.482188889439134</v>
+        <v>1.317564537631675</v>
       </c>
       <c r="F239" t="n">
-        <v>8.981169534111476</v>
+        <v>4.986763845159937</v>
       </c>
       <c r="G239" t="n">
-        <v>1.232373234572589</v>
+        <v>0</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I239" t="n">
-        <v>37</v>
+        <v>998</v>
       </c>
     </row>
     <row r="240">
@@ -9079,22 +9079,22 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>43587</v>
+        <v>43494</v>
       </c>
       <c r="C240" t="n">
         <v>6.479343508161802</v>
       </c>
       <c r="D240" t="n">
-        <v>4.623030203083925</v>
+        <v>4.900526077133267</v>
       </c>
       <c r="E240" t="n">
-        <v>1.856313305077877</v>
+        <v>1.578817431028535</v>
       </c>
       <c r="F240" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="G240" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -9112,22 +9112,22 @@
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>44207</v>
+        <v>43525</v>
       </c>
       <c r="C241" t="n">
+        <v>6.479343508161802</v>
+      </c>
+      <c r="D241" t="n">
+        <v>4.98648224894669</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1.492861259215111</v>
+      </c>
+      <c r="F241" t="n">
         <v>8.981169534111476</v>
       </c>
-      <c r="D241" t="n">
-        <v>4.960222696133116</v>
-      </c>
-      <c r="E241" t="n">
-        <v>4.020946837978361</v>
-      </c>
-      <c r="F241" t="n">
-        <v>7.344381400446302</v>
-      </c>
       <c r="G241" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="242">
@@ -9145,22 +9145,22 @@
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>44251</v>
+        <v>43542</v>
       </c>
       <c r="C242" t="n">
+        <v>6.479343508161802</v>
+      </c>
+      <c r="D242" t="n">
+        <v>4.948813908130575</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1.530529600031227</v>
+      </c>
+      <c r="F242" t="n">
         <v>8.981169534111476</v>
       </c>
-      <c r="D242" t="n">
-        <v>4.83408159290553</v>
-      </c>
-      <c r="E242" t="n">
-        <v>4.147087941205946</v>
-      </c>
-      <c r="F242" t="n">
-        <v>7.344381400446302</v>
-      </c>
       <c r="G242" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -9178,22 +9178,22 @@
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>44316</v>
+        <v>43544</v>
       </c>
       <c r="C243" t="n">
+        <v>6.479343508161802</v>
+      </c>
+      <c r="D243" t="n">
+        <v>4.927512009062117</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1.551831499099685</v>
+      </c>
+      <c r="F243" t="n">
         <v>8.981169534111476</v>
       </c>
-      <c r="D243" t="n">
-        <v>4.848904144559079</v>
-      </c>
-      <c r="E243" t="n">
-        <v>4.132265389552397</v>
-      </c>
-      <c r="F243" t="n">
-        <v>7.344381400446302</v>
-      </c>
       <c r="G243" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -9211,22 +9211,22 @@
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>44407</v>
+        <v>43549</v>
       </c>
       <c r="C244" t="n">
+        <v>6.479343508161802</v>
+      </c>
+      <c r="D244" t="n">
+        <v>4.997154618722668</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1.482188889439134</v>
+      </c>
+      <c r="F244" t="n">
         <v>8.981169534111476</v>
       </c>
-      <c r="D244" t="n">
-        <v>4.836772685935765</v>
-      </c>
-      <c r="E244" t="n">
-        <v>4.144396848175711</v>
-      </c>
-      <c r="F244" t="n">
-        <v>7.344381400446302</v>
-      </c>
       <c r="G244" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="245">
@@ -9244,22 +9244,22 @@
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>44412</v>
+        <v>43587</v>
       </c>
       <c r="C245" t="n">
+        <v>6.479343508161802</v>
+      </c>
+      <c r="D245" t="n">
+        <v>4.623030203083925</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1.856313305077877</v>
+      </c>
+      <c r="F245" t="n">
         <v>8.981169534111476</v>
       </c>
-      <c r="D245" t="n">
-        <v>4.8860963466692</v>
-      </c>
-      <c r="E245" t="n">
-        <v>4.095073187442276</v>
-      </c>
-      <c r="F245" t="n">
-        <v>7.344381400446302</v>
-      </c>
       <c r="G245" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -9277,22 +9277,22 @@
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>44414</v>
+        <v>44207</v>
       </c>
       <c r="C246" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D246" t="n">
-        <v>4.786847454410559</v>
+        <v>4.960222696133116</v>
       </c>
       <c r="E246" t="n">
-        <v>4.194322079700918</v>
+        <v>4.020946837978361</v>
       </c>
       <c r="F246" t="n">
         <v>7.344381400446302</v>
       </c>
       <c r="G246" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>207</v>
+        <v>32</v>
       </c>
     </row>
     <row r="247">
@@ -9310,22 +9310,22 @@
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>44627</v>
+        <v>44251</v>
       </c>
       <c r="C247" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D247" t="n">
-        <v>4.937009236682012</v>
+        <v>4.83408159290553</v>
       </c>
       <c r="E247" t="n">
-        <v>4.044160297429464</v>
+        <v>4.147087941205946</v>
       </c>
       <c r="F247" t="n">
         <v>7.344381400446302</v>
       </c>
       <c r="G247" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -9343,22 +9343,22 @@
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>44726</v>
+        <v>44316</v>
       </c>
       <c r="C248" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D248" t="n">
-        <v>4.97403584109406</v>
+        <v>4.848904144559079</v>
       </c>
       <c r="E248" t="n">
-        <v>4.007133693017416</v>
+        <v>4.132265389552397</v>
       </c>
       <c r="F248" t="n">
         <v>7.344381400446302</v>
       </c>
       <c r="G248" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="249">
@@ -9376,22 +9376,22 @@
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>44782</v>
+        <v>44407</v>
       </c>
       <c r="C249" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D249" t="n">
-        <v>4.902950456519259</v>
+        <v>4.836772685935765</v>
       </c>
       <c r="E249" t="n">
-        <v>4.078219077592218</v>
+        <v>4.144396848175711</v>
       </c>
       <c r="F249" t="n">
         <v>7.344381400446302</v>
       </c>
       <c r="G249" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -9409,22 +9409,22 @@
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>45180</v>
+        <v>44412</v>
       </c>
       <c r="C250" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D250" t="n">
-        <v>4.951254377199697</v>
+        <v>4.8860963466692</v>
       </c>
       <c r="E250" t="n">
-        <v>4.029915156911779</v>
+        <v>4.095073187442276</v>
       </c>
       <c r="F250" t="n">
         <v>7.344381400446302</v>
       </c>
       <c r="G250" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -9442,22 +9442,22 @@
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>45189</v>
+        <v>44414</v>
       </c>
       <c r="C251" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D251" t="n">
-        <v>4.993140260854316</v>
+        <v>4.786847454410559</v>
       </c>
       <c r="E251" t="n">
-        <v>3.98802927325716</v>
+        <v>4.194322079700918</v>
       </c>
       <c r="F251" t="n">
         <v>7.344381400446302</v>
       </c>
       <c r="G251" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>23</v>
+        <v>207</v>
       </c>
     </row>
     <row r="252">
@@ -9475,22 +9475,22 @@
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>45215</v>
+        <v>44627</v>
       </c>
       <c r="C252" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D252" t="n">
-        <v>4.84814916820575</v>
+        <v>4.937009236682012</v>
       </c>
       <c r="E252" t="n">
-        <v>4.133020365905726</v>
+        <v>4.044160297429464</v>
       </c>
       <c r="F252" t="n">
         <v>7.344381400446302</v>
       </c>
       <c r="G252" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -9508,22 +9508,22 @@
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>45511</v>
+        <v>44726</v>
       </c>
       <c r="C253" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D253" t="n">
-        <v>4.929721731225539</v>
+        <v>4.97403584109406</v>
       </c>
       <c r="E253" t="n">
-        <v>4.051447802885937</v>
+        <v>4.007133693017416</v>
       </c>
       <c r="F253" t="n">
-        <v>5.362557977629486</v>
+        <v>7.344381400446302</v>
       </c>
       <c r="G253" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="254">
@@ -9541,22 +9541,22 @@
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>45526</v>
+        <v>44782</v>
       </c>
       <c r="C254" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D254" t="n">
-        <v>4.988568063108893</v>
+        <v>4.902950456519259</v>
       </c>
       <c r="E254" t="n">
-        <v>3.992601471002583</v>
+        <v>4.078219077592218</v>
       </c>
       <c r="F254" t="n">
-        <v>5.362557977629486</v>
+        <v>7.344381400446302</v>
       </c>
       <c r="G254" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="255">
@@ -9574,22 +9574,22 @@
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>45545</v>
+        <v>45180</v>
       </c>
       <c r="C255" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D255" t="n">
-        <v>4.982074895595809</v>
+        <v>4.951254377199697</v>
       </c>
       <c r="E255" t="n">
-        <v>3.999094638515667</v>
+        <v>4.029915156911779</v>
       </c>
       <c r="F255" t="n">
-        <v>5.362557977629486</v>
+        <v>7.344381400446302</v>
       </c>
       <c r="G255" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -9607,22 +9607,22 @@
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>45558</v>
+        <v>45189</v>
       </c>
       <c r="C256" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D256" t="n">
-        <v>4.982535591207016</v>
+        <v>4.993140260854316</v>
       </c>
       <c r="E256" t="n">
-        <v>3.99863394290446</v>
+        <v>3.98802927325716</v>
       </c>
       <c r="F256" t="n">
-        <v>5.362557977629486</v>
+        <v>7.344381400446302</v>
       </c>
       <c r="G256" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257">
@@ -9640,22 +9640,22 @@
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>45560</v>
+        <v>45215</v>
       </c>
       <c r="C257" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D257" t="n">
-        <v>4.925789435560072</v>
+        <v>4.84814916820575</v>
       </c>
       <c r="E257" t="n">
-        <v>4.055380098551405</v>
+        <v>4.133020365905726</v>
       </c>
       <c r="F257" t="n">
-        <v>5.362557977629486</v>
+        <v>7.344381400446302</v>
       </c>
       <c r="G257" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
@@ -9673,22 +9673,22 @@
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>45572</v>
+        <v>45511</v>
       </c>
       <c r="C258" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D258" t="n">
-        <v>4.984457289107501</v>
+        <v>4.929721731225539</v>
       </c>
       <c r="E258" t="n">
-        <v>3.996712245003976</v>
+        <v>4.051447802885937</v>
       </c>
       <c r="F258" t="n">
         <v>5.362557977629486</v>
       </c>
       <c r="G258" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -9706,55 +9706,55 @@
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>45594</v>
+        <v>45526</v>
       </c>
       <c r="C259" t="n">
         <v>8.981169534111476</v>
       </c>
       <c r="D259" t="n">
-        <v>4.928418851954757</v>
+        <v>4.988568063108893</v>
       </c>
       <c r="E259" t="n">
-        <v>4.052750682156719</v>
+        <v>3.992601471002583</v>
       </c>
       <c r="F259" t="n">
-        <v>4.928418851954757</v>
+        <v>5.362557977629486</v>
       </c>
       <c r="G259" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I259" t="n">
-        <v>302</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ZM US Equity</t>
+          <t>XYZ US Equity</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>44413</v>
+        <v>45545</v>
       </c>
       <c r="C260" t="n">
-        <v>5.015863051287561</v>
+        <v>8.981169534111476</v>
       </c>
       <c r="D260" t="n">
-        <v>4.908292136290467</v>
+        <v>4.982074895595809</v>
       </c>
       <c r="E260" t="n">
-        <v>0.107570914997094</v>
+        <v>3.999094638515667</v>
       </c>
       <c r="F260" t="n">
-        <v>10.89725045662099</v>
+        <v>5.362557977629486</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -9762,32 +9762,32 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>105</v>
+        <v>8</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ZM US Equity</t>
+          <t>XYZ US Equity</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>44519</v>
+        <v>45558</v>
       </c>
       <c r="C261" t="n">
-        <v>5.015863051287561</v>
+        <v>8.981169534111476</v>
       </c>
       <c r="D261" t="n">
-        <v>4.99786642206161</v>
+        <v>4.982535591207016</v>
       </c>
       <c r="E261" t="n">
-        <v>0.01799662922595147</v>
+        <v>3.99863394290446</v>
       </c>
       <c r="F261" t="n">
-        <v>10.89725045662099</v>
+        <v>5.362557977629486</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -9795,39 +9795,204 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
+          <t>XYZ US Equity</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>45560</v>
+      </c>
+      <c r="C262" t="n">
+        <v>8.981169534111476</v>
+      </c>
+      <c r="D262" t="n">
+        <v>4.925789435560072</v>
+      </c>
+      <c r="E262" t="n">
+        <v>4.055380098551405</v>
+      </c>
+      <c r="F262" t="n">
+        <v>5.362557977629486</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1.060020615169871</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Recovered to Large</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>XYZ US Equity</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>45572</v>
+      </c>
+      <c r="C263" t="n">
+        <v>8.981169534111476</v>
+      </c>
+      <c r="D263" t="n">
+        <v>4.984457289107501</v>
+      </c>
+      <c r="E263" t="n">
+        <v>3.996712245003976</v>
+      </c>
+      <c r="F263" t="n">
+        <v>5.362557977629486</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1.060020615169871</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Recovered to Large</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>XYZ US Equity</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>45594</v>
+      </c>
+      <c r="C264" t="n">
+        <v>8.981169534111476</v>
+      </c>
+      <c r="D264" t="n">
+        <v>4.928418851954757</v>
+      </c>
+      <c r="E264" t="n">
+        <v>4.052750682156719</v>
+      </c>
+      <c r="F264" t="n">
+        <v>4.928418851954757</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1.060020615169871</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Still Residual</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
           <t>ZM US Equity</t>
         </is>
       </c>
-      <c r="B262" s="2" t="n">
+      <c r="B265" s="2" t="n">
+        <v>44413</v>
+      </c>
+      <c r="C265" t="n">
+        <v>5.015863051287561</v>
+      </c>
+      <c r="D265" t="n">
+        <v>4.908292136290467</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.107570914997094</v>
+      </c>
+      <c r="F265" t="n">
+        <v>10.89725045662099</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Recovered to Large</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ZM US Equity</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>44519</v>
+      </c>
+      <c r="C266" t="n">
+        <v>5.015863051287561</v>
+      </c>
+      <c r="D266" t="n">
+        <v>4.99786642206161</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.01799662922595147</v>
+      </c>
+      <c r="F266" t="n">
+        <v>10.89725045662099</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Recovered to Large</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ZM US Equity</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="C262" t="n">
+      <c r="C267" t="n">
         <v>10.89725045662099</v>
       </c>
-      <c r="D262" t="n">
+      <c r="D267" t="n">
         <v>4.779458771669474</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E267" t="n">
         <v>6.117791684951515</v>
       </c>
-      <c r="F262" t="n">
+      <c r="F267" t="n">
         <v>4.833918425186428</v>
       </c>
-      <c r="G262" t="n">
+      <c r="G267" t="n">
         <v>0</v>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H267" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
       </c>
-      <c r="I262" t="n">
+      <c r="I267" t="n">
         <v>186</v>
       </c>
     </row>
@@ -9842,7 +10007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10198,381 +10363,381 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIDU US Equity</t>
+          <t>BABA US Equity</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>43690</v>
+        <v>43363</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>44176</v>
+        <v>45925</v>
       </c>
       <c r="D19" t="n">
-        <v>486</v>
+        <v>2562</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1774855932996128</v>
+        <v>0.1555838802032586</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CRSP US Equity</t>
+          <t>BIDU US Equity</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>43220</v>
+        <v>43690</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>43252</v>
+        <v>44176</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>486</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2671023170990939</v>
+        <v>0.1774855932996128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DDD US Equity</t>
+          <t>BIDU US Equity</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>42794</v>
+        <v>44334</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>44512</v>
+        <v>45925</v>
       </c>
       <c r="D21" t="n">
-        <v>1718</v>
+        <v>1591</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2516488494639003</v>
+        <v>0.1536917164820487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXAS US Equity</t>
+          <t>CRSP US Equity</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45475</v>
+        <v>43220</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45877</v>
+        <v>43252</v>
       </c>
       <c r="D22" t="n">
-        <v>402</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8467072203452185</v>
+        <v>0.2671023170990939</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FANUY US Equity</t>
+          <t>DDD US Equity</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>42398</v>
+        <v>42794</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>42948</v>
+        <v>44512</v>
       </c>
       <c r="D23" t="n">
-        <v>550</v>
+        <v>1718</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4875444081657636</v>
+        <v>0.2516488494639003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GM US Equity</t>
+          <t>EXAS US Equity</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>42829</v>
+        <v>45475</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>43033</v>
+        <v>45877</v>
       </c>
       <c r="D24" t="n">
-        <v>204</v>
+        <v>402</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4913143939062111</v>
+        <v>0.8467072203452185</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOOG US Equity</t>
+          <t>FANUY US Equity</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>42142</v>
+        <v>42398</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>42458</v>
+        <v>42948</v>
       </c>
       <c r="D25" t="n">
-        <v>316</v>
+        <v>550</v>
       </c>
       <c r="E25" t="n">
-        <v>1.968287853227933</v>
+        <v>0.4875444081657636</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ICE US Equity</t>
+          <t>GM US Equity</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>43427</v>
+        <v>42829</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>44062</v>
+        <v>43033</v>
       </c>
       <c r="D26" t="n">
-        <v>635</v>
+        <v>204</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4197300085576299</v>
+        <v>0.4913143939062111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ILMN US Equity</t>
+          <t>GOOG US Equity</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>44140</v>
+        <v>42142</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45600</v>
+        <v>42458</v>
       </c>
       <c r="D27" t="n">
-        <v>1460</v>
+        <v>316</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1631762599743918</v>
+        <v>1.968287853227933</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INTU US Equity</t>
+          <t>ICE US Equity</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>42199</v>
+        <v>43427</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>42915</v>
+        <v>44062</v>
       </c>
       <c r="D28" t="n">
-        <v>716</v>
+        <v>635</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4960517874846671</v>
+        <v>0.4197300085576299</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IOVA US Equity</t>
+          <t>ILMN US Equity</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>43909</v>
+        <v>44140</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>43983</v>
+        <v>45600</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>1460</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4817989418673881</v>
+        <v>0.1631762599743918</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IRDM US Equity</t>
+          <t>INTU US Equity</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>44610</v>
+        <v>42199</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45700</v>
+        <v>42915</v>
       </c>
       <c r="D30" t="n">
-        <v>1090</v>
+        <v>716</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2451590244595243</v>
+        <v>0.4960517874846671</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LC US Equity</t>
+          <t>IOVA US Equity</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>42108</v>
+        <v>43909</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42373</v>
+        <v>43983</v>
       </c>
       <c r="D31" t="n">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2484844303043602</v>
+        <v>0.4817989418673881</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LC US Equity</t>
+          <t>IRDM US Equity</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>42389</v>
+        <v>44610</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>42510</v>
+        <v>45700</v>
       </c>
       <c r="D32" t="n">
-        <v>121</v>
+        <v>1090</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4798186261651735</v>
+        <v>0.2451590244595243</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MBBYF US Equity</t>
+          <t>LC US Equity</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>42041</v>
+        <v>42108</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>42312</v>
+        <v>42373</v>
       </c>
       <c r="D33" t="n">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2530496535245101</v>
+        <v>0.2484844303043602</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MDSO US Equity</t>
+          <t>LC US Equity</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>42458</v>
+        <v>42389</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>42836</v>
+        <v>42510</v>
       </c>
       <c r="D34" t="n">
-        <v>378</v>
+        <v>121</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4980202279847413</v>
+        <v>0.4798186261651735</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>MBBYF US Equity</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>42402</v>
+        <v>42041</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>43250</v>
+        <v>42312</v>
       </c>
       <c r="D35" t="n">
-        <v>848</v>
+        <v>271</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5014902113002812</v>
+        <v>0.2530496535245101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>MDSO US Equity</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>43389</v>
+        <v>42458</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>43720</v>
+        <v>42836</v>
       </c>
       <c r="D36" t="n">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5042868338863414</v>
+        <v>0.4980202279847413</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>META US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>43277</v>
+        <v>42402</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>43633</v>
+        <v>43250</v>
       </c>
       <c r="D37" t="n">
-        <v>356</v>
+        <v>848</v>
       </c>
       <c r="E37" t="n">
-        <v>1.015456084431241</v>
+        <v>0.5014902113002812</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>META US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>43690</v>
+        <v>43389</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>44050</v>
+        <v>43720</v>
       </c>
       <c r="D38" t="n">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="E38" t="n">
-        <v>1.128319817305769</v>
+        <v>0.5042868338863414</v>
       </c>
     </row>
     <row r="39">
@@ -10582,662 +10747,662 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>44152</v>
+        <v>43277</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>45090</v>
+        <v>43633</v>
       </c>
       <c r="D39" t="n">
-        <v>938</v>
+        <v>356</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5117047168118555</v>
+        <v>1.015456084431241</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NTDOY US Equity</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>43217</v>
+        <v>43690</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>44064</v>
+        <v>44050</v>
       </c>
       <c r="D40" t="n">
-        <v>847</v>
+        <v>360</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07378429246598177</v>
+        <v>1.128319817305769</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NVDA US Equity</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>43941</v>
+        <v>44152</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>44708</v>
+        <v>45090</v>
       </c>
       <c r="D41" t="n">
-        <v>767</v>
+        <v>938</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4049662906836736</v>
+        <v>0.5117047168118555</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NVDA US Equity</t>
+          <t>NTDOY US Equity</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>44937</v>
+        <v>43217</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>45755</v>
+        <v>44064</v>
       </c>
       <c r="D42" t="n">
-        <v>818</v>
+        <v>847</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3305475183913147</v>
+        <v>0.07378429246598177</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PACB US Equity</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>42065</v>
+        <v>43941</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>43110</v>
+        <v>44708</v>
       </c>
       <c r="D43" t="n">
-        <v>1045</v>
+        <v>767</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4621782788964639</v>
+        <v>0.4049662906836736</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PACB US Equity</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>43427</v>
+        <v>44937</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>44061</v>
+        <v>45755</v>
       </c>
       <c r="D44" t="n">
-        <v>634</v>
+        <v>818</v>
       </c>
       <c r="E44" t="n">
-        <v>0.003631100790811985</v>
+        <v>0.3305475183913147</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PINS US Equity</t>
+          <t>PACB US Equity</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>44271</v>
+        <v>42065</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>45278</v>
+        <v>43110</v>
       </c>
       <c r="D45" t="n">
-        <v>1007</v>
+        <v>1045</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1841894457298311</v>
+        <v>0.4621782788964639</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PLTR US Equity</t>
+          <t>PACB US Equity</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>44620</v>
+        <v>43427</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>45057</v>
+        <v>44061</v>
       </c>
       <c r="D46" t="n">
-        <v>437</v>
+        <v>634</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5108595090123392</v>
+        <v>0.003631100790811985</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRLB US Equity</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>43277</v>
+        <v>44271</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>43508</v>
+        <v>45278</v>
       </c>
       <c r="D47" t="n">
-        <v>231</v>
+        <v>1007</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3038956856049196</v>
+        <v>0.1841894457298311</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>43220</v>
+        <v>44620</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>43861</v>
+        <v>45057</v>
       </c>
       <c r="D48" t="n">
-        <v>641</v>
+        <v>437</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5054318209415705</v>
+        <v>0.5108595090123392</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PRLB US Equity</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>43909</v>
+        <v>43277</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>44139</v>
+        <v>43508</v>
       </c>
       <c r="D49" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E49" t="n">
-        <v>1.011077438029077</v>
+        <v>0.3038956856049196</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QCOM US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>42041</v>
+        <v>43220</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>42437</v>
+        <v>43861</v>
       </c>
       <c r="D50" t="n">
-        <v>396</v>
+        <v>641</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5063940383503459</v>
+        <v>0.5054318209415705</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QCOM US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>42492</v>
+        <v>43909</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>42761</v>
+        <v>44139</v>
       </c>
       <c r="D51" t="n">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9564386412945145</v>
+        <v>1.011077438029077</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>REGN US Equity</t>
+          <t>QCOM US Equity</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>43718</v>
+        <v>42041</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>44208</v>
+        <v>42437</v>
       </c>
       <c r="D52" t="n">
-        <v>490</v>
+        <v>396</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1485730774152069</v>
+        <v>0.5063940383503459</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCHW US Equity</t>
+          <t>QCOM US Equity</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>42004</v>
+        <v>42492</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>42510</v>
+        <v>42761</v>
       </c>
       <c r="D53" t="n">
-        <v>506</v>
+        <v>269</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5009728625923319</v>
+        <v>0.9564386412945145</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>REGN US Equity</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>43909</v>
+        <v>43718</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>44062</v>
+        <v>44208</v>
       </c>
       <c r="D54" t="n">
-        <v>153</v>
+        <v>490</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5073047995186792</v>
+        <v>0.1485730774152069</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>SCHW US Equity</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>44487</v>
+        <v>42004</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>44593</v>
+        <v>42510</v>
       </c>
       <c r="D55" t="n">
-        <v>106</v>
+        <v>506</v>
       </c>
       <c r="E55" t="n">
-        <v>0.02795461985489596</v>
+        <v>0.5009728625923319</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>44035</v>
+        <v>44062</v>
       </c>
       <c r="D56" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4945624760246113</v>
+        <v>0.5073047995186792</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>44077</v>
+        <v>44487</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>44235</v>
+        <v>44593</v>
       </c>
       <c r="D57" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5279001378718579</v>
+        <v>0.02795461985489596</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SPOT US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>43718</v>
+        <v>43909</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>43978</v>
+        <v>44035</v>
       </c>
       <c r="D58" t="n">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4853398926368807</v>
+        <v>0.4945624760246113</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TCEHY US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>43909</v>
+        <v>44077</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>44076</v>
+        <v>44235</v>
       </c>
       <c r="D59" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E59" t="n">
-        <v>0.123539086270048</v>
+        <v>0.5279001378718579</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>SPOT US Equity</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>43909</v>
+        <v>43718</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>44049</v>
+        <v>43978</v>
       </c>
       <c r="D60" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9832553552772862</v>
+        <v>0.4853398926368807</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TER US Equity</t>
+          <t>TCEHY US Equity</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>44125</v>
+        <v>43909</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>44228</v>
+        <v>44076</v>
       </c>
       <c r="D61" t="n">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1473049641047281</v>
+        <v>0.123539086270048</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TER US Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>44474</v>
+        <v>43909</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>45090</v>
+        <v>44049</v>
       </c>
       <c r="D62" t="n">
-        <v>616</v>
+        <v>140</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03768149071833461</v>
+        <v>0.9832553552772862</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TER US Equity</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>43193</v>
+        <v>44125</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>43312</v>
+        <v>44228</v>
       </c>
       <c r="D63" t="n">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E63" t="n">
-        <v>1.050984313232082</v>
+        <v>0.1473049641047281</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TRMB US Equity</t>
+          <t>TER US Equity</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>42383</v>
+        <v>44474</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>44291</v>
+        <v>45090</v>
       </c>
       <c r="D64" t="n">
-        <v>1908</v>
+        <v>616</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1589357122174727</v>
+        <v>0.03768149071833461</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TSM US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>43397</v>
+        <v>43193</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>44021</v>
+        <v>43312</v>
       </c>
       <c r="D65" t="n">
-        <v>624</v>
+        <v>119</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3591561354308993</v>
+        <v>1.050984313232082</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TSM US Equity</t>
+          <t>TRMB US Equity</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>44313</v>
+        <v>42383</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>45797</v>
+        <v>44291</v>
       </c>
       <c r="D66" t="n">
-        <v>1484</v>
+        <v>1908</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4103560491936882</v>
+        <v>0.1589357122174727</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTD US Equity</t>
+          <t>TSM US Equity</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>43901</v>
+        <v>43397</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>45243</v>
+        <v>44021</v>
       </c>
       <c r="D67" t="n">
-        <v>1342</v>
+        <v>624</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5068798618366805</v>
+        <v>0.3591561354308993</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>TSM US Equity</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>43040</v>
+        <v>44313</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>44021</v>
+        <v>45797</v>
       </c>
       <c r="D68" t="n">
-        <v>981</v>
+        <v>1484</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4945969629745466</v>
+        <v>0.4103560491936882</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TWOUQ US Equity</t>
+          <t>TTD US Equity</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>43217</v>
+        <v>43901</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>43411</v>
+        <v>45243</v>
       </c>
       <c r="D69" t="n">
-        <v>194</v>
+        <v>1342</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5237886032674073</v>
+        <v>0.5068798618366805</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>42408</v>
+        <v>43040</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>42562</v>
+        <v>44021</v>
       </c>
       <c r="D70" t="n">
-        <v>154</v>
+        <v>981</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4892660769048036</v>
+        <v>0.4945969629745466</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWOUQ US Equity</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>43927</v>
+        <v>43217</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>44250</v>
+        <v>43411</v>
       </c>
       <c r="D71" t="n">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="E71" t="n">
-        <v>0.276087329749161</v>
+        <v>0.5237886032674073</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>USD Curncy</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>42004</v>
+        <v>42408</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>42041</v>
+        <v>42562</v>
       </c>
       <c r="D72" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.4892660769048036</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>XLNX US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>42397</v>
+        <v>43927</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>42766</v>
+        <v>44250</v>
       </c>
       <c r="D73" t="n">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9656078142539634</v>
+        <v>0.276087329749161</v>
       </c>
     </row>
     <row r="74">
@@ -11247,34 +11412,53 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>43389</v>
+        <v>42397</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>43581</v>
+        <v>42766</v>
       </c>
       <c r="D74" t="n">
-        <v>192</v>
+        <v>369</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4992442592796971</v>
+        <v>0.9656078142539634</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>XLNX US Equity</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>43389</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>43581</v>
+      </c>
+      <c r="D75" t="n">
+        <v>192</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.4992442592796971</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Z US Equity</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B76" s="2" t="n">
         <v>42375</v>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C76" s="2" t="n">
         <v>43320</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D76" t="n">
         <v>945</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E76" t="n">
         <v>1.22404643619271</v>
       </c>
     </row>
